--- a/static/data/exports/Retro_JK_AE_2008.xlsx
+++ b/static/data/exports/Retro_JK_AE_2008.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/static/data/exports/Retro_JK_AE_2008.xlsx
+++ b/static/data/exports/Retro_JK_AE_2008.xlsx
@@ -20061,11 +20061,11 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>1934125</v>
+        <v>1934124</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Mohd. Sadiq Gujar</t>
+          <t>Shuban Ji</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -20098,7 +20098,7 @@
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>Mohd. Sadiq Gujar</t>
+          <t>Shuban Ji</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
@@ -20123,11 +20123,11 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>1934124</v>
+        <v>1934125</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Shuban Ji</t>
+          <t>Mohd. Sadiq Gujar</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -20160,7 +20160,7 @@
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>Shuban Ji</t>
+          <t>Mohd. Sadiq Gujar</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
@@ -20247,20 +20247,20 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>1934127</v>
+        <v>1934128</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Jayant Kumar Shakdar</t>
+          <t>Saira Sameer</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>JKDPN</t>
+          <t>NCP</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>24870</v>
+        <v>24837</v>
       </c>
       <c r="E320" t="n">
         <v>31</v>
@@ -20284,12 +20284,12 @@
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>Jayant Kumar Shakdar</t>
+          <t>Saira Sameer</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>JKDPN</t>
+          <t>NCP</t>
         </is>
       </c>
       <c r="Q320" t="b">
@@ -20309,20 +20309,20 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>1934128</v>
+        <v>1934127</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Saira Sameer</t>
+          <t>Jayant Kumar Shakdar</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>NCP</t>
+          <t>JKDPN</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>24837</v>
+        <v>24870</v>
       </c>
       <c r="E321" t="n">
         <v>31</v>
@@ -20346,12 +20346,12 @@
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>Saira Sameer</t>
+          <t>Jayant Kumar Shakdar</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>NCP</t>
+          <t>JKDPN</t>
         </is>
       </c>
       <c r="Q321" t="b">
@@ -21735,20 +21735,20 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>1934151</v>
+        <v>1934152</v>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Sona Ullah Tamiri</t>
+          <t>Wali Mohd. Khan</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>24808</v>
+        <v>24898</v>
       </c>
       <c r="E344" t="n">
         <v>41</v>
@@ -21772,12 +21772,12 @@
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t>Sona Ullah Tamiri</t>
+          <t>Wali Mohd. Khan</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="Q344" t="b">
@@ -21797,20 +21797,20 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>1934152</v>
+        <v>1934151</v>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Wali Mohd. Khan</t>
+          <t>Sona Ullah Tamiri</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>24898</v>
+        <v>24808</v>
       </c>
       <c r="E345" t="n">
         <v>41</v>
@@ -21834,12 +21834,12 @@
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t>Wali Mohd. Khan</t>
+          <t>Sona Ullah Tamiri</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q345" t="b">
@@ -25294,20 +25294,20 @@
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>1934205</v>
+        <v>1934204</v>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Tanveer Hasan Ganai</t>
+          <t>Mohammad Yousuf Naikoo</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>RJD</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>24890</v>
+        <v>24898</v>
       </c>
       <c r="E397" t="n">
         <v>37</v>
@@ -25331,12 +25331,12 @@
       </c>
       <c r="K397" t="inlineStr">
         <is>
-          <t>Tanveer Hasan Ganai</t>
+          <t>Mohammad Yousuf Naikoo</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>RJD</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="Q397" t="b">
@@ -25356,20 +25356,20 @@
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>1934204</v>
+        <v>1934205</v>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Mohammad Yousuf Naikoo</t>
+          <t>Tanveer Hasan Ganai</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>RJD</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>24898</v>
+        <v>24890</v>
       </c>
       <c r="E398" t="n">
         <v>37</v>
@@ -25393,12 +25393,12 @@
       </c>
       <c r="K398" t="inlineStr">
         <is>
-          <t>Mohammad Yousuf Naikoo</t>
+          <t>Tanveer Hasan Ganai</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>RJD</t>
         </is>
       </c>
       <c r="Q398" t="b">
@@ -34541,11 +34541,11 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D546" t="n">
-        <v>24876</v>
+        <v>24857</v>
       </c>
       <c r="E546" t="n">
         <v>2366</v>
@@ -35905,11 +35905,11 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D568" t="n">
-        <v>24876</v>
+        <v>24857</v>
       </c>
       <c r="E568" t="n">
         <v>1652</v>
@@ -37765,11 +37765,11 @@
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D598" t="n">
-        <v>24876</v>
+        <v>24857</v>
       </c>
       <c r="E598" t="n">
         <v>17175</v>
@@ -39067,11 +39067,11 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D619" t="n">
-        <v>24876</v>
+        <v>24857</v>
       </c>
       <c r="E619" t="n">
         <v>3782</v>
@@ -41361,11 +41361,11 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D656" t="n">
-        <v>24876</v>
+        <v>24857</v>
       </c>
       <c r="E656" t="n">
         <v>4941</v>
@@ -42725,11 +42725,11 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D678" t="n">
-        <v>24876</v>
+        <v>24857</v>
       </c>
       <c r="E678" t="n">
         <v>820</v>
@@ -49970,20 +49970,20 @@
     </row>
     <row r="795">
       <c r="A795" t="n">
-        <v>1934603</v>
+        <v>1934602</v>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>Rehamtullah</t>
+          <t>Ajaz Ahmed Lone</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>JKDPN</t>
+          <t>BSP</t>
         </is>
       </c>
       <c r="D795" t="n">
-        <v>24870</v>
+        <v>24827</v>
       </c>
       <c r="E795" t="n">
         <v>211</v>
@@ -50007,12 +50007,12 @@
       </c>
       <c r="K795" t="inlineStr">
         <is>
-          <t>Rehamtullah</t>
+          <t>Ajaz Ahmed Lone</t>
         </is>
       </c>
       <c r="L795" t="inlineStr">
         <is>
-          <t>JKDPN</t>
+          <t>BSP</t>
         </is>
       </c>
       <c r="Q795" t="b">
@@ -50032,20 +50032,20 @@
     </row>
     <row r="796">
       <c r="A796" t="n">
-        <v>1934602</v>
+        <v>1934603</v>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>Ajaz Ahmed Lone</t>
+          <t>Rehamtullah</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>BSP</t>
+          <t>JKDPN</t>
         </is>
       </c>
       <c r="D796" t="n">
-        <v>24827</v>
+        <v>24870</v>
       </c>
       <c r="E796" t="n">
         <v>211</v>
@@ -50069,12 +50069,12 @@
       </c>
       <c r="K796" t="inlineStr">
         <is>
-          <t>Ajaz Ahmed Lone</t>
+          <t>Rehamtullah</t>
         </is>
       </c>
       <c r="L796" t="inlineStr">
         <is>
-          <t>BSP</t>
+          <t>JKDPN</t>
         </is>
       </c>
       <c r="Q796" t="b">
@@ -54257,11 +54257,11 @@
       </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D864" t="n">
-        <v>24876</v>
+        <v>24857</v>
       </c>
       <c r="E864" t="n">
         <v>558</v>
@@ -62069,11 +62069,11 @@
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D990" t="n">
-        <v>24876</v>
+        <v>24857</v>
       </c>
       <c r="E990" t="n">
         <v>320</v>
@@ -69134,20 +69134,20 @@
     </row>
     <row r="1102">
       <c r="A1102" t="n">
-        <v>1934910</v>
+        <v>1934909</v>
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t>Swarn Sharma</t>
+          <t>Brij Mohan</t>
         </is>
       </c>
       <c r="C1102" t="inlineStr">
         <is>
-          <t>JSM(P)</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D1102" t="n">
-        <v>24884</v>
+        <v>24808</v>
       </c>
       <c r="E1102" t="n">
         <v>76</v>
@@ -69171,12 +69171,12 @@
       </c>
       <c r="K1102" t="inlineStr">
         <is>
-          <t>Swarn Sharma</t>
+          <t>Brij Mohan</t>
         </is>
       </c>
       <c r="L1102" t="inlineStr">
         <is>
-          <t>JSM(P)</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q1102" t="b">
@@ -69196,20 +69196,20 @@
     </row>
     <row r="1103">
       <c r="A1103" t="n">
-        <v>1934909</v>
+        <v>1934910</v>
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t>Brij Mohan</t>
+          <t>Swarn Sharma</t>
         </is>
       </c>
       <c r="C1103" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>JSM(P)</t>
         </is>
       </c>
       <c r="D1103" t="n">
-        <v>24808</v>
+        <v>24884</v>
       </c>
       <c r="E1103" t="n">
         <v>76</v>
@@ -69233,12 +69233,12 @@
       </c>
       <c r="K1103" t="inlineStr">
         <is>
-          <t>Brij Mohan</t>
+          <t>Swarn Sharma</t>
         </is>
       </c>
       <c r="L1103" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>JSM(P)</t>
         </is>
       </c>
       <c r="Q1103" t="b">
@@ -69258,20 +69258,20 @@
     </row>
     <row r="1104">
       <c r="A1104" t="n">
-        <v>1934911</v>
+        <v>1934912</v>
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t>Om Parkash Sadotra</t>
+          <t>Sanjeev Kumar</t>
         </is>
       </c>
       <c r="C1104" t="inlineStr">
         <is>
-          <t>BHBP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D1104" t="n">
-        <v>24885</v>
+        <v>24808</v>
       </c>
       <c r="E1104" t="n">
         <v>70</v>
@@ -69295,12 +69295,12 @@
       </c>
       <c r="K1104" t="inlineStr">
         <is>
-          <t>Om Parkash Sadotra</t>
+          <t>Sanjeev Kumar</t>
         </is>
       </c>
       <c r="L1104" t="inlineStr">
         <is>
-          <t>BHBP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q1104" t="b">
@@ -69320,20 +69320,20 @@
     </row>
     <row r="1105">
       <c r="A1105" t="n">
-        <v>1934912</v>
+        <v>1934911</v>
       </c>
       <c r="B1105" t="inlineStr">
         <is>
-          <t>Sanjeev Kumar</t>
+          <t>Om Parkash Sadotra</t>
         </is>
       </c>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BHBP</t>
         </is>
       </c>
       <c r="D1105" t="n">
-        <v>24808</v>
+        <v>24885</v>
       </c>
       <c r="E1105" t="n">
         <v>70</v>
@@ -69357,12 +69357,12 @@
       </c>
       <c r="K1105" t="inlineStr">
         <is>
-          <t>Sanjeev Kumar</t>
+          <t>Om Parkash Sadotra</t>
         </is>
       </c>
       <c r="L1105" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BHBP</t>
         </is>
       </c>
       <c r="Q1105" t="b">
